--- a/Result/profitability/1442.xlsx
+++ b/Result/profitability/1442.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.19</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8512500000000001</v>
+        <v>0.6537499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>45.29125</v>
+        <v>46.3575</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.41</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6449999999999999</v>
+        <v>0.5425</v>
       </c>
       <c r="N3" t="n">
-        <v>44.115</v>
+        <v>44.51625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.24</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6375</v>
+        <v>0.5349999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>41.925</v>
+        <v>42.04125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1018,13 +1018,13 @@
         <v>0.45</v>
       </c>
       <c r="M5" t="n">
-        <v>0.53125</v>
+        <v>0.49875</v>
       </c>
       <c r="N5" t="n">
-        <v>38.85375</v>
+        <v>38.87875</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.03</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4424999999999999</v>
+        <v>0.445</v>
       </c>
       <c r="N6" t="n">
-        <v>34.8775</v>
+        <v>35.1575</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.25</v>
       </c>
       <c r="M7" t="n">
-        <v>0.41625</v>
+        <v>0.41</v>
       </c>
       <c r="N7" t="n">
-        <v>31.85125</v>
+        <v>31.95875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.54</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4175</v>
+        <v>0.44875</v>
       </c>
       <c r="N8" t="n">
-        <v>28.7875</v>
+        <v>28.79125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1442</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>530</v>
+      </c>
+      <c r="D75" t="n">
+        <v>266</v>
+      </c>
+      <c r="E75" t="n">
+        <v>265</v>
+      </c>
+      <c r="F75" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="G75" t="n">
+        <v>201</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>37.85%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>202</v>
+      </c>
+      <c r="K75" t="n">
+        <v>176</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.8875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.08695652173913</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.03000000000000114</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.0006015640665730793</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.3513513513513513</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.1999999999999957</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.004024144869215096</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
